--- a/experiment/Omni_2CH_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/Omni_2CH_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.02</v>
+        <v>23.03</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5331</v>
+        <v>0.5344</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>25.87</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7533</v>
+        <v>0.7516</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>25.43</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6373</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.43</v>
+        <v>26.4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5818</v>
+        <v>0.5810999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.61</v>
+        <v>23.63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7385</v>
+        <v>0.7409</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.89</v>
+        <v>32.93</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7943</v>
+        <v>0.7957</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.3</v>
+        <v>28.35</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8193</v>
+        <v>0.8213</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.82</v>
+        <v>33.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9211</v>
+        <v>0.9226</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.43</v>
+        <v>32.5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8638</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>27.39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7504</v>
+        <v>0.7507</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.87</v>
+        <v>32.97</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9443</v>
+        <v>0.9453</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.26</v>
+        <v>34.3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8798</v>
+        <v>0.8808</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.66</v>
+        <v>26.72</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9486</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.38</v>
+        <v>27.37</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7788</v>
+        <v>0.7786999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.61</v>
+        <v>28.62</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7825</v>
       </c>
     </row>
   </sheetData>
